--- a/AAII_Financials/Quarterly/GS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>GS</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="28" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="29" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20236000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16912000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15577000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14845000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14199000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14775000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13518000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12302000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12449000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13895000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10741000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11810000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10280000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12395000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20930000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18482000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14981000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14318000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13854000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15161000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16698000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19276000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13304000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12629000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15385000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12180000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14141000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13014000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14351000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13406000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13213000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>13025000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>13554000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>13392000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11587000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>11087000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>10503000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>10308000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>10283000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>9926000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3687000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3098000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2813000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2513000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2485000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2356000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2395000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2199000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2154000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1967000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1959000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1920000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1867000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1871000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11771000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7824000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4434000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2629000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2405000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2692000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2435000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2828000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2873000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2759000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3035000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4412000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4671000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5304000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5512000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5141000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5307000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4919000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4730000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4156000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3811000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3306000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3095000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2845000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2714000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2388000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>16549000</v>
+      </c>
+      <c r="E10" s="3">
         <v>13814000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12764000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12332000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11714000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12419000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11123000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10103000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10295000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11928000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8782000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9890000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8413000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10524000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9159000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10658000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10547000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11689000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11449000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>12469000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14263000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16448000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10431000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9870000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12350000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>7768000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9470000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7710000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8839000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8265000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7906000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8106000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8824000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>9236000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7776000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7781000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>7408000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7463000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>7569000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>7538000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,8 +1222,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1332,8 +1345,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1454,53 +1470,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E14" s="3">
         <v>42000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>114000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>131000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>116000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-11000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>26000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>41000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>224000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>103000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-322000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>959000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1008000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>462000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1522,21 +1541,21 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>293000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>278000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1590000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>937000</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1552,14 +1571,14 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1576,130 +1595,136 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E15" s="3">
         <v>495000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>507000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>531000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>503000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>506000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>470000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>621000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>526000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>547000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1525000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>568000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>605000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>580000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>727000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>666000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>570000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>492000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>488000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>509000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>520000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>498000</v>
       </c>
       <c r="Y15" s="3">
         <v>498000</v>
       </c>
       <c r="Z15" s="3">
+        <v>498000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>468000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>499000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>437000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>464000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>473000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>399000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>368000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>377000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>317000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>335000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>299000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>350000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>280000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>265000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>257000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>267000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>247000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1739,252 +1764,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11701000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10384000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9608000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9322000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9125000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9139000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8235000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8274000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8309000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8555000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8809000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8095000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7536000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7940000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19400000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14726000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11437000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9662000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8829000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8319000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9858000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10939000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7763000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8330000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14094000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10832000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11820000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10598000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11224000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10687000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10505000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9947000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10278000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9973000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8479000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8111000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>7994000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>7769000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6886000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>7058000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8535000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6528000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5969000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5523000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5074000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5636000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5283000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4028000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4140000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5340000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1932000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3715000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2744000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4455000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1530000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3756000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3544000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4656000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5025000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6842000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6840000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8337000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5541000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4299000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1291000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1348000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2321000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2416000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3127000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2719000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2708000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3078000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3276000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3419000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3108000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2976000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2509000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2539000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3397000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2868000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2027,8 +2059,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2071,8 +2104,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2149,130 +2182,136 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9044000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7023000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6476000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6054000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5577000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6142000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5753000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4649000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4666000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5887000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3457000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4283000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3349000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5035000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2257000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4422000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4114000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5148000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5513000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7351000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7360000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8835000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6039000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4767000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1790000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2785000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2889000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3526000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3087000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3085000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3395000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3611000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3718000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3458000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3256000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2774000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2796000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3664000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3115000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2315,8 +2354,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2393,252 +2432,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8563000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6486000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5855000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5392000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4958000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5647000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5257000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3987000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3916000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5237000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2254000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2756000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1736000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3993000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1530000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3756000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3544000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4656000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5025000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6842000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6840000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8337000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5541000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4299000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1291000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1348000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2321000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2416000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3127000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2719000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2708000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3078000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3276000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3419000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3108000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2976000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2509000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2539000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3397000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2868000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1935000</v>
+      </c>
+      <c r="E24" s="3">
         <v>856000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1238000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1294000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1235000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>909000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1146000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>997000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>873000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1105000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>246000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>698000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>520000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>759000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>204000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>687000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>617000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>717000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1090000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1464000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1354000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1501000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1035000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>932000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>918000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>135000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>404000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>539000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>706000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>468000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>657000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>554000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>711000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>587000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>636000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>848000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>678000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>284000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1050000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>774000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2759,252 +2807,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6628000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5630000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4617000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4098000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3723000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4738000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4111000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2990000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3043000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4132000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2008000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2058000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1216000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3234000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1326000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3069000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2927000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3939000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3935000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5378000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5486000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6836000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4506000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3367000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>373000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1213000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1917000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1877000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2421000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2251000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2051000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2524000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2565000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2832000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2472000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2128000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1831000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2255000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2347000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2094000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>5391000</v>
+        <v>6382000</v>
       </c>
       <c r="E27" s="3">
+        <v>5388000</v>
+      </c>
+      <c r="F27" s="3">
         <v>4369000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3845000</v>
       </c>
-      <c r="G27" s="3">
-        <v>3460000</v>
-      </c>
       <c r="H27" s="3">
+        <v>3461000</v>
+      </c>
+      <c r="I27" s="3">
         <v>4570000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3914000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2767000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2874000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3921000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1857000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1868000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1054000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3077000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1185000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2962000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2786000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3831000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3809000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5284000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5347000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6711000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4362000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3233000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>197000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1123000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1793000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2198000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2182000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1835000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2453000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2348000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2737000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2257000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2035000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2162000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2153000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2100000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3125,8 +3182,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3199,8 +3259,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3217,24 +3277,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>487000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-4400000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3247,8 +3307,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3369,8 +3432,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3491,8 +3557,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3535,8 +3604,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3613,130 +3682,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6628000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5630000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4617000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4098000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3723000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4738000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4111000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2990000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3043000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4132000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2008000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2058000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1216000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3234000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1185000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2962000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2786000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3831000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3809000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5284000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5347000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6711000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4362000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3233000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>197000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1123000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1724000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1793000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2198000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2182000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2322000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2453000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2348000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2737000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2143000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2035000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2162000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2153000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2100000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3857,257 +3932,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6628000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5630000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4617000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4098000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3723000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4738000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4111000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2990000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3043000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4132000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2008000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2058000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1216000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3234000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1185000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2962000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2786000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3831000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3809000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5284000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5347000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6711000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4362000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3233000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>197000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1123000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1724000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1793000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2198000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2182000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2322000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2453000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2348000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2737000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2143000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2035000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2162000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2153000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2100000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4150,8 +4234,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4194,175 +4279,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>187266000</v>
+      </c>
+      <c r="E41" s="3">
         <v>179530000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>164259000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>169577000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>152967000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>167408000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>182092000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>154689000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>206326000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>209385000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>241577000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>239879000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>270931000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>229327000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>241825000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>284251000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>288606000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>274164000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>261036000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>211830000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>240289000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>191155000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>155842000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>153201000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>132599000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>105489000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>133546000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>94094000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>91092000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>87884000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>130547000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>118871000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>131417000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>120503000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>110051000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>116610000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>110888000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>123035000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>121711000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>137191000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>969588000</v>
+      </c>
+      <c r="E42" s="3">
         <v>962670000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>832370000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>840780000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>830209000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>863755000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>796845000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>881341000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>807642000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>840801000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>790168000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>738274000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>697639000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>730796000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4438,130 +4527,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>507008000</v>
+      </c>
+      <c r="E43" s="3">
         <v>477842000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>439229000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>410261000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>414130000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>388794000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>343436000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>350467000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>342190000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>356495000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>328027000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>330407000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>346975000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>337496000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>138826000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>169526000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>167408000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>178633000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>164598000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>174901000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>165423000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>167600000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>123969000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>113850000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>109394000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>123825000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>77003000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>86004000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>86846000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>76170000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>82900000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>86157000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>92116000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>111443000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>87886000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>91135000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>96246000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>83802000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>69371000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>83460000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4604,8 +4699,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4682,53 +4777,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>185318000</v>
+      </c>
+      <c r="E45" s="3">
         <v>181418000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>158765000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>159400000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>165120000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>130444000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>148934000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>137463000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>117838000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>114066000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111085000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>99086000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>91470000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>81927000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4804,53 +4902,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1849180000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1801460000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1594623000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1580018000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1562426000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1550401000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1471307000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1523960000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1473996000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1520747000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1470857000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1407646000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1407015000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1379546000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4926,374 +5027,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>259835000</v>
+      </c>
+      <c r="E47" s="3">
         <v>241694000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>198382000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>207097000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>205912000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>199149000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>187974000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>186710000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>164014000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>158180000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>150229000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>146950000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>138891000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>131790000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1033123000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1073222000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1115775000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1108553000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1012245000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1027557000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>951995000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>911909000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>852048000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>832930000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>865348000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>827292000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>750541000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>742681000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>689789000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>687846000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>645019000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>678075000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>669213000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>666623000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>644814000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>644728000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>624148000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>615364000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>588043000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>577568000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9425000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9504000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9524000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9798000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9831000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9891000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9991000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10576000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8418000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12595000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13415000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15303000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17617000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18609000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19246000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19234000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20705000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20625000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20386000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20459000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23140000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24757000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>25427000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>25783000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26045000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>25904000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>24246000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>23590000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>22657000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>21663000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18317000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18302000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17108000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>15777000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>15094000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>14805000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>13978000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>13372000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12070000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>11347000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9271000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7522000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6791000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6814000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6840000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6740000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6700000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6834000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6885000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6918000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7093000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7254000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7863000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8404000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8383000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8251000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8210000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6481000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4703000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4823000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4855000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4907000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4962000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4965000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4792000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4810000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4837000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4886000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4114000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4092000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4082000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4101000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4106000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4049000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4038000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4058000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4080000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4067000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4095000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>4104000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5414,8 +5527,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5536,8 +5652,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5547,12 +5666,12 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>4255000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5580,86 +5699,89 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3">
         <v>396000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1510000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>520000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>985000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1020000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3660000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2220000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1220000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>780000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1330000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3345000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2436000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2795000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2640000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2685000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2365000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2356000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2675000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2053000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2371000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4362000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5958000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5538000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5592000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5550000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>5630000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5780,130 +5902,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2127711000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2060180000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1809320000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1807982000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1785009000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1766181000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1675972000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1728080000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1653313000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1698440000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1641594000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1577153000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1571386000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1538349000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1441799000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1555994000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1601224000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1589441000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1463988000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1443230000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1387922000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1301548000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1163028000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1132059000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1141523000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1089756000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>992968000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1007320000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>944903000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>925349000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>931796000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>957190000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>968610000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>973535000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>916776000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>930132000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>906518000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>894069000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>860165000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>879987000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5946,8 +6074,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5990,419 +6119,429 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300057000</v>
+      </c>
+      <c r="E57" s="3">
         <v>293039000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>231865000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>256835000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>259252000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>253799000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>223255000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>250355000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>242986000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>256662000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>230728000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>252342000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>257843000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>266301000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>262045000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>278457000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>279984000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>292981000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>251931000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>252120000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>238697000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>224268000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>190658000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>187357000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>199211000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>213178000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>174817000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>188161000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>185279000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>180997000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>180235000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>189968000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>192617000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>190991000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>178169000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>202986000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>199562000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>196258000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>188455000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>204487000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>536091000</v>
+      </c>
+      <c r="E58" s="3">
         <v>511390000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>449582000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>443495000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>443646000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>468227000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>496339000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>481299000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>456527000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>479735000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>450598000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>414167000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>399465000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>372071000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>595541000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>657539000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>668738000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>662877000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>632740000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>601001000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>573040000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>524647000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>474242000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>439557000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>429943000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>384848000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>378242000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>362607000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>307913000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>299683000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>298845000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>309113000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>305396000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>309373000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>285140000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>275426000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>262232000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>263583000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>248297000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>256468000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>329239000</v>
+      </c>
+      <c r="E59" s="3">
         <v>379786000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>341153000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>235026000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>263180000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>269329000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>131119000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>202159000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>211353000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>231734000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>146548000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>176717000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>186579000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>192300000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12048000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20027000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19501000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16928000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23632000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>25550000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22290000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20897000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13334000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21444000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22722000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17101000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12221000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17636000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16290000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14487000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9698000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14516000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14049000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11477000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>16194000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13038000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>11309000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>9652000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>13195000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>12515000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1200583000</v>
+        <v>1182759000</v>
       </c>
       <c r="E60" s="3">
+        <v>1197956000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1043262000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>953729000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>982374000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1005348000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>868910000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>951049000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>926882000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>982465000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>846135000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>857634000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>857140000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>842503000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6478,178 +6617,184 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>361394000</v>
+      </c>
+      <c r="E61" s="3">
         <v>328277000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>298001000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>287723000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>288543000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>271412000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>251636000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>260435000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>245217000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>242860000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>249774000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>232238000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>238883000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>249714000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>254245000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>248116000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>258966000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>267265000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>263466000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>252365000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>251254000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>231498000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>226018000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>227189000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>236224000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>244699000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>219158000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>228723000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>231723000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>237275000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>236027000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>242132000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>239387000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>236673000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>227579000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>223707000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>215993000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>210497000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>197491000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>197876000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>407584000</v>
+        <v>459649000</v>
       </c>
       <c r="E62" s="3">
+        <v>410074000</v>
+      </c>
+      <c r="F62" s="3">
         <v>342639000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>441779000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>389653000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>364765000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>433013000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>394959000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>361336000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>354239000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>428417000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>369533000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>358339000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>328002000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>337000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6668,36 +6813,36 @@
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z62" s="3">
         <v>478000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD62" s="3">
         <v>415000</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3">
         <v>344000</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6713,8 +6858,8 @@
       <c r="AM62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN62" s="3">
-        <v>0</v>
+      <c r="AN62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO62" s="3">
         <v>0</v>
@@ -6722,8 +6867,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6844,8 +6992,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6966,8 +7117,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7088,130 +7242,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2003985000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1936444000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1683902000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1683231000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1660570000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1641525000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1553559000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1606443000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1533435000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1579564000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1524326000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1459405000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1454362000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1420219000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1324610000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1436704000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1483353000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1474202000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1354062000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1336933000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1286032000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1203884000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1067096000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1039409000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1051494000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>997377000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>902703000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>915308000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>854011000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>835076000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>841611000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>870428000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>882011000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>889956000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>834533000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>843840000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>819843000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>807152000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>773272000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>792877000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7254,8 +7414,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7376,8 +7537,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7498,16 +7662,19 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>13028000</v>
+      </c>
+      <c r="E70" s="3">
         <v>13703000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>15153000</v>
       </c>
       <c r="F70" s="3">
         <v>15153000</v>
@@ -7519,16 +7686,16 @@
         <v>15153000</v>
       </c>
       <c r="I70" s="3">
-        <v>13253000</v>
+        <v>15153000</v>
       </c>
       <c r="J70" s="3">
         <v>13253000</v>
       </c>
       <c r="K70" s="3">
+        <v>13253000</v>
+      </c>
+      <c r="L70" s="3">
         <v>12753000</v>
-      </c>
-      <c r="L70" s="3">
-        <v>11203000</v>
       </c>
       <c r="M70" s="3">
         <v>11203000</v>
@@ -7537,7 +7704,7 @@
         <v>11203000</v>
       </c>
       <c r="O70" s="3">
-        <v>10703000</v>
+        <v>11203000</v>
       </c>
       <c r="P70" s="3">
         <v>10703000</v>
@@ -7558,16 +7725,16 @@
         <v>10703000</v>
       </c>
       <c r="V70" s="3">
+        <v>10703000</v>
+      </c>
+      <c r="W70" s="3">
         <v>9953000</v>
-      </c>
-      <c r="W70" s="3">
-        <v>9203000</v>
       </c>
       <c r="X70" s="3">
         <v>9203000</v>
       </c>
       <c r="Y70" s="3">
-        <v>11203000</v>
+        <v>9203000</v>
       </c>
       <c r="Z70" s="3">
         <v>11203000</v>
@@ -7603,10 +7770,10 @@
         <v>11203000</v>
       </c>
       <c r="AK70" s="3">
+        <v>11203000</v>
+      </c>
+      <c r="AL70" s="3">
         <v>11853000</v>
-      </c>
-      <c r="AL70" s="3">
-        <v>11203000</v>
       </c>
       <c r="AM70" s="3">
         <v>11203000</v>
@@ -7620,8 +7787,11 @@
       <c r="AP70" s="3">
         <v>11203000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>11203000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7742,130 +7912,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>174352000</v>
+      </c>
+      <c r="E72" s="3">
         <v>169316000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>165288000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>162143000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>159535000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>157019000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>153412000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>150454000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>148652000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>146690000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>143688000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>142743000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>141798000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>141591000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>139372000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>139067000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>136998000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>134931000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>131811000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>128631000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>124051000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>119210000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>112947000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>109033000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>106248000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>106501000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>106465000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>105194000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>103867000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>101988000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>100100000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>98083000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>95941000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>93907000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>91519000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>93958000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>92225000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>90904000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>89039000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>87160000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7986,8 +8162,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8108,8 +8287,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8230,130 +8412,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>109714000</v>
+      </c>
+      <c r="E76" s="3">
         <v>109079000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>109819000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>109249000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>108943000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>109147000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>108743000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>107947000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>106710000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>107343000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>105702000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>106074000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>105790000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>106806000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>106486000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>108587000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>107168000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>104536000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>99223000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>96344000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>92687000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>88461000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>84729000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>81447000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>78826000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>81176000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>79062000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>80809000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>79689000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>79070000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>78982000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>75559000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>75396000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>72376000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>70390000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>75089000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>75472000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>75714000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>75690000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>75907000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8474,257 +8662,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6628000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5630000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4617000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4098000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3723000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4738000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4111000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2990000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3043000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4132000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2008000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2058000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1216000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3234000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1185000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2962000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2786000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3831000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3809000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5284000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5347000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6711000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4362000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3233000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>197000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1123000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1724000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1793000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2198000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2182000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2322000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2453000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2348000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2737000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2143000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2035000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2162000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2153000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2100000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8767,130 +8964,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E83" s="3">
         <v>485000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>520000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>505000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>514000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>521000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1525000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>557000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>528000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>807000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>482000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>519000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>473000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>727000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>666000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>570000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>492000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>488000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>509000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>520000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>498000</v>
       </c>
       <c r="Y83" s="3">
         <v>498000</v>
       </c>
       <c r="Z83" s="3">
+        <v>498000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>468000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>499000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>437000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>464000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>473000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>399000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>368000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>377000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>317000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>335000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>299000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>350000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>280000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>265000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>257000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>267000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>247000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9011,8 +9212,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9133,8 +9337,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9255,8 +9462,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9377,8 +9587,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9499,130 +9712,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6105000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-31868000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16276000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2680000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5672000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37230000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>46766000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-38060000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6120000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28038000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28358000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25534000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31901000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9404000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-33162000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16010000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>45394000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-19534000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30274000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-39260000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>20467000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5183000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>16014000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>34936000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-11647000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-53031000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>51351000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>9439000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-45006000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>18101000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5314000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8598000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-964000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-6623000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2734000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-10489000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-3364000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3935000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-4577000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9665,130 +9884,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-502000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-565000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-531000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-558000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-476000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-499000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-586000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-466000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-542000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-497000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-546000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-507000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-666000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-597000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-754000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-990000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1051000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-953000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1119000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-883000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1353000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1312000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1403000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-998000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1065000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2046000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2040000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2128000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2035000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2196000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2188000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1563000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-975000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-688000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-683000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1676000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1626000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1642000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9909,8 +10132,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10031,130 +10257,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28572000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56307000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5033000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5113000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11334000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22747000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7115000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29286000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5243000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7980000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3342000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8033000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3959000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1978000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6292000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14159000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-38488000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17021000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13938000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4819000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9221000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2487000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8923000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>2996000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>3907000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-32336000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4840000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-17894000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1985000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4032000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3590000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-9213000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-10810000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-10887000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5395000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1547000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2032000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1513000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10197,8 +10429,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10241,86 +10474,89 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-872000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-890000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-716000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-707000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-693000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-701000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-441000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-447000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-448000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-450000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-449000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-453000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-466000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-319000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-306000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-305000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-311000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-531000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-376000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-498000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-395000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-510000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-366000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-468000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-378000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10441,8 +10677,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10563,8 +10802,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10685,192 +10927,198 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>30916000</v>
+      </c>
+      <c r="E100" s="3">
         <v>104294000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16755000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19781000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13262000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>42826000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7817000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10340000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2371000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7171000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>28016000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6442000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13886000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-20544000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9576000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1621000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>14456000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>53101000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>38247000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>15620000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>37888000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>42983000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4450000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-17330000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>34850000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>57310000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7059000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>12812000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-6230000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3844000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-583000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3200000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>5906000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>20629000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>11094000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>14140000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>3711000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>6261000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>2077000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>1655000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4483000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2467000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4431000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5369000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1565000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3345000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5382000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3927000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-224000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>620000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6604000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7827000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6920000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3418000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6604000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7827000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6920000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3418000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -10929,126 +11177,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7736000</v>
+      </c>
+      <c r="E102" s="3">
         <v>15271000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5318000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16610000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14441000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14684000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>27403000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-51637000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3059000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-32192000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1698000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31052000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>41604000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12498000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-42426000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4355000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14442000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13128000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>49206000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-28459000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>49134000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>35313000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2641000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>20602000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>27110000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-28057000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39452000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3002000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3208000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-42663000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>11676000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-12546000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>10914000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>10452000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-6559000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>5722000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-12147000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1324000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>3708000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-4513000</v>
       </c>
     </row>
